--- a/data/nutrient_coverage_comparison.xlsx
+++ b/data/nutrient_coverage_comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/faridannam/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/faridannam/Desktop/indonesia_fct/datasets/2_process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F95D89-7F79-FA45-8DFB-C46C5E238B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5D27F8-655B-7445-B8BB-15E6CB5F3AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3500" yWindow="600" windowWidth="34900" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nutrient Coverage" sheetId="1" r:id="rId1"/>
@@ -625,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -666,23 +666,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -695,6 +678,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,27 +1007,27 @@
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.1640625" style="26" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" style="17" customWidth="1"/>
     <col min="12" max="12" width="190.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
@@ -1060,13 +1054,13 @@
       <c r="H2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="13" t="s">
@@ -1074,7 +1068,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="24" t="s">
         <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1098,21 +1092,21 @@
       <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1131,24 +1125,24 @@
       <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="28" t="s">
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="20" t="s">
+      <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="23"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
@@ -1170,19 +1164,19 @@
       <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="J5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="28" t="s">
+      <c r="K5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="20"/>
+      <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="4" t="s">
         <v>30</v>
       </c>
@@ -1201,22 +1195,22 @@
       <c r="G6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="28" t="s">
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="20"/>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
@@ -1235,22 +1229,22 @@
       <c r="G7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="28" t="s">
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="20"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="4" t="s">
         <v>37</v>
       </c>
@@ -1269,22 +1263,22 @@
       <c r="G8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="28" t="s">
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="20"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
@@ -1303,22 +1297,22 @@
       <c r="G9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="K9" s="28" t="s">
+      <c r="K9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="L9" s="20"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="24" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1342,19 +1336,19 @@
       <c r="H10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="20"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="1" t="s">
         <v>48</v>
       </c>
@@ -1376,21 +1370,21 @@
       <c r="H11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="28" t="s">
+      <c r="J11" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="4" t="s">
         <v>53</v>
       </c>
@@ -1412,19 +1406,19 @@
       <c r="H12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="28" t="s">
+      <c r="K12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="20"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="1" t="s">
         <v>56</v>
       </c>
@@ -1446,21 +1440,21 @@
       <c r="H13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="28" t="s">
+      <c r="J13" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L13" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="4" t="s">
         <v>60</v>
       </c>
@@ -1482,21 +1476,21 @@
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="28" t="s">
+      <c r="J14" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="L14" s="20" t="s">
+      <c r="L14" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="1" t="s">
         <v>64</v>
       </c>
@@ -1518,21 +1512,21 @@
       <c r="H15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="28" t="s">
+      <c r="J15" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="4" t="s">
         <v>68</v>
       </c>
@@ -1554,19 +1548,19 @@
       <c r="H16" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="J16" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="K16" s="28" t="s">
+      <c r="K16" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="L16" s="20"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="1" t="s">
         <v>71</v>
       </c>
@@ -1588,21 +1582,21 @@
       <c r="H17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L17" s="20" t="s">
+      <c r="I17" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="4" t="s">
         <v>73</v>
       </c>
@@ -1624,21 +1618,21 @@
       <c r="H18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L18" s="20" t="s">
+      <c r="I18" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="1" t="s">
         <v>75</v>
       </c>
@@ -1660,21 +1654,21 @@
       <c r="H19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" s="20" t="s">
+      <c r="I19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="4" t="s">
         <v>76</v>
       </c>
@@ -1696,21 +1690,21 @@
       <c r="H20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="20" t="s">
+      <c r="I20" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="4" t="s">
         <v>77</v>
       </c>
@@ -1732,21 +1726,21 @@
       <c r="H21" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L21" s="20" t="s">
+      <c r="I21" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>79</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1767,22 +1761,22 @@
       <c r="G22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="28" t="s">
+      <c r="H22" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="28" t="s">
+      <c r="J22" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K22" s="28" t="s">
+      <c r="K22" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="L22" s="20"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="4" t="s">
         <v>83</v>
       </c>
@@ -1801,22 +1795,22 @@
       <c r="G23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="28" t="s">
+      <c r="H23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="28" t="s">
+      <c r="J23" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="K23" s="28" t="s">
+      <c r="K23" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="L23" s="20"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
@@ -1838,19 +1832,19 @@
       <c r="H24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="J24" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L24" s="20"/>
+      <c r="J24" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="1" t="s">
         <v>88</v>
       </c>
@@ -1872,19 +1866,19 @@
       <c r="H25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="28" t="s">
+      <c r="I25" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="20" t="s">
+      <c r="K25" s="19"/>
+      <c r="L25" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="4" t="s">
         <v>91</v>
       </c>
@@ -1906,21 +1900,21 @@
       <c r="H26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="28" t="s">
+      <c r="I26" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="K26" s="28" t="s">
+      <c r="K26" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="L26" s="19" t="s">
+      <c r="L26" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="1" t="s">
         <v>95</v>
       </c>
@@ -1942,21 +1936,21 @@
       <c r="H27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="J27" s="28" t="s">
+      <c r="J27" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="K27" s="28" t="s">
+      <c r="K27" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="4" t="s">
         <v>99</v>
       </c>
@@ -1978,19 +1972,19 @@
       <c r="H28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="J28" s="28" t="s">
+      <c r="J28" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="L28" s="20"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
+      <c r="A29" s="26"/>
       <c r="B29" s="1" t="s">
         <v>102</v>
       </c>
@@ -2012,19 +2006,19 @@
       <c r="H29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="J29" s="28" t="s">
+      <c r="J29" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="K29" s="28" t="s">
+      <c r="K29" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="L29" s="20"/>
+      <c r="L29" s="4"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
+      <c r="A30" s="26"/>
       <c r="B30" s="4" t="s">
         <v>105</v>
       </c>
@@ -2046,21 +2040,21 @@
       <c r="H30" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I30" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J30" s="28" t="s">
+      <c r="I30" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J30" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="K30" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L30" s="20" t="s">
+      <c r="K30" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="1" t="s">
         <v>108</v>
       </c>
@@ -2082,21 +2076,21 @@
       <c r="H31" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J31" s="28" t="s">
+      <c r="I31" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="K31" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L31" s="19" t="s">
+      <c r="K31" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L31" s="15" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
+      <c r="A32" s="26"/>
       <c r="B32" s="4" t="s">
         <v>111</v>
       </c>
@@ -2118,21 +2112,21 @@
       <c r="H32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="28" t="s">
+      <c r="I32" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="K32" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L32" s="19" t="s">
+      <c r="K32" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="15" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="1" t="s">
         <v>114</v>
       </c>
@@ -2154,19 +2148,19 @@
       <c r="H33" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="I33" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J33" s="28" t="s">
+      <c r="J33" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="K33" s="28" t="s">
+      <c r="K33" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="L33" s="20"/>
+      <c r="L33" s="4"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="4" t="s">
         <v>118</v>
       </c>
@@ -2188,21 +2182,21 @@
       <c r="H34" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I34" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34" s="28" t="s">
+      <c r="I34" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J34" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="K34" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L34" s="19" t="s">
+      <c r="K34" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
+      <c r="A35" s="25"/>
       <c r="B35" s="1" t="s">
         <v>121</v>
       </c>
@@ -2224,19 +2218,19 @@
       <c r="H35" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K35" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="L35" s="20"/>
+      <c r="I35" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="L35" s="4"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="24" t="s">
         <v>122</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -2260,19 +2254,19 @@
       <c r="H36" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I36" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J36" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K36" s="28" t="s">
+      <c r="I36" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K36" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L36" s="4"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
+      <c r="A37" s="26"/>
       <c r="B37" s="4" t="s">
         <v>124</v>
       </c>
@@ -2294,19 +2288,19 @@
       <c r="H37" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I37" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J37" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K37" s="28" t="s">
+      <c r="I37" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L37" s="4"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
+      <c r="A38" s="26"/>
       <c r="B38" s="4" t="s">
         <v>125</v>
       </c>
@@ -2328,19 +2322,19 @@
       <c r="H38" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I38" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J38" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K38" s="28" t="s">
+      <c r="I38" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K38" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L38" s="4"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
+      <c r="A39" s="26"/>
       <c r="B39" s="4" t="s">
         <v>126</v>
       </c>
@@ -2362,19 +2356,19 @@
       <c r="H39" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J39" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K39" s="28" t="s">
+      <c r="I39" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K39" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
+      <c r="A40" s="26"/>
       <c r="B40" s="4" t="s">
         <v>127</v>
       </c>
@@ -2396,19 +2390,19 @@
       <c r="H40" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I40" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J40" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K40" s="28" t="s">
+      <c r="I40" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="23"/>
+      <c r="A41" s="26"/>
       <c r="B41" s="4" t="s">
         <v>128</v>
       </c>
@@ -2430,19 +2424,19 @@
       <c r="H41" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I41" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J41" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K41" s="28" t="s">
+      <c r="I41" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="24"/>
+      <c r="A42" s="25"/>
       <c r="B42" s="4" t="s">
         <v>129</v>
       </c>
@@ -2464,19 +2458,19 @@
       <c r="H42" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J42" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K42" s="28" t="s">
+      <c r="I42" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L42" s="4"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="24" t="s">
         <v>130</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2500,19 +2494,19 @@
       <c r="H43" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J43" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K43" s="28" t="s">
+      <c r="I43" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L43" s="4"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
+      <c r="A44" s="25"/>
       <c r="B44" s="4" t="s">
         <v>132</v>
       </c>
@@ -2534,19 +2528,19 @@
       <c r="H44" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J44" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K44" s="28" t="s">
+      <c r="I44" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K44" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L44" s="4"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="24" t="s">
         <v>133</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2567,16 +2561,16 @@
       <c r="G45" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="28" t="s">
+      <c r="H45" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="J45" s="28" t="s">
+      <c r="J45" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="K45" s="28" t="s">
+      <c r="K45" s="19" t="s">
         <v>50</v>
       </c>
       <c r="L45" s="14" t="s">
@@ -2584,7 +2578,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="24"/>
+      <c r="A46" s="25"/>
       <c r="B46" s="4" t="s">
         <v>139</v>
       </c>
@@ -2606,13 +2600,13 @@
       <c r="H46" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I46" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J46" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K46" s="28" t="s">
+      <c r="I46" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K46" s="19" t="s">
         <v>142</v>
       </c>
       <c r="L46" s="15" t="s">
@@ -2628,29 +2622,29 @@
       <c r="B49" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="10"/>
